--- a/templates/innovation-calculators.xlsx
+++ b/templates/innovation-calculators.xlsx
@@ -22,7 +22,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -96,17 +101,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -471,7 +482,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -518,7 +529,7 @@
           <t>Spend per customer per year</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>360</v>
       </c>
     </row>
@@ -555,7 +566,7 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="6">
         <f>B5*B6</f>
         <v/>
       </c>
@@ -566,7 +577,7 @@
           <t>SAM</t>
         </is>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="6">
         <f>B7*B6</f>
         <v/>
       </c>
@@ -577,13 +588,14 @@
           <t>SOM</t>
         </is>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="6">
         <f>B8*B6</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -591,7 +603,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -623,153 +635,154 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Likely wrong (1-5)</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Damage if wrong (1-5)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Experiment</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Pass mark</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Assumption 1</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="9">
         <f>B7*C7</f>
         <v/>
       </c>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="9" t="inlineStr"/>
+      <c r="E7" s="10" t="inlineStr"/>
+      <c r="F7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Assumption 2</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="9">
         <f>B8*C8</f>
         <v/>
       </c>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="9" t="inlineStr"/>
+      <c r="E8" s="10" t="inlineStr"/>
+      <c r="F8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Assumption 3</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="9">
         <f>B9*C9</f>
         <v/>
       </c>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="9" t="inlineStr"/>
+      <c r="E9" s="10" t="inlineStr"/>
+      <c r="F9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Assumption 4</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="9">
         <f>B10*C10</f>
         <v/>
       </c>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="9" t="inlineStr"/>
+      <c r="E10" s="10" t="inlineStr"/>
+      <c r="F10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Assumption 5</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="9">
         <f>B11*C11</f>
         <v/>
       </c>
-      <c r="E11" s="9" t="inlineStr"/>
-      <c r="F11" s="9" t="inlineStr"/>
+      <c r="E11" s="10" t="inlineStr"/>
+      <c r="F11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Assumption 6</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="9">
         <f>B12*C12</f>
         <v/>
       </c>
-      <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="9" t="inlineStr"/>
+      <c r="E12" s="10" t="inlineStr"/>
+      <c r="F12" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -777,7 +790,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -814,7 +827,7 @@
           <t>Monthly price per customer</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="11" t="n">
         <v>30</v>
       </c>
     </row>
@@ -824,7 +837,7 @@
           <t>Gross margin (0-1)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="12" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -834,7 +847,7 @@
           <t>Monthly churn (0-1)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="12" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -844,7 +857,7 @@
           <t>Sales and marketing spend per month</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>30000</v>
       </c>
     </row>
@@ -864,7 +877,7 @@
           <t>Cash in the bank</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="5" t="n">
         <v>900000</v>
       </c>
     </row>
@@ -874,8 +887,8 @@
           <t>Cash in per month</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
-        <v>45000</v>
+      <c r="B11" s="5" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="12">
@@ -884,8 +897,8 @@
           <t>Cash out per month</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>105000</v>
+      <c r="B12" s="5" t="n">
+        <v>96000</v>
       </c>
     </row>
     <row r="13">
@@ -894,7 +907,7 @@
           <t>MRR (monthly recurring revenue)</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="5" t="n">
         <v>36000</v>
       </c>
     </row>
@@ -911,7 +924,7 @@
           <t>CAC</t>
         </is>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="6">
         <f>B8/B9</f>
         <v/>
       </c>
@@ -922,7 +935,7 @@
           <t>LTV</t>
         </is>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="6">
         <f>(B5*B6)/B7</f>
         <v/>
       </c>
@@ -933,7 +946,7 @@
           <t>LTV ÷ CAC</t>
         </is>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="13">
         <f>B17/B16</f>
         <v/>
       </c>
@@ -949,7 +962,7 @@
           <t>CAC payback (months)</t>
         </is>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="14">
         <f>B16/(B5*B6)</f>
         <v/>
       </c>
@@ -965,7 +978,7 @@
           <t>Net burn per month</t>
         </is>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="6">
         <f>B12-B11</f>
         <v/>
       </c>
@@ -976,7 +989,7 @@
           <t>Runway (months)</t>
         </is>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="14">
         <f>B10/B20</f>
         <v/>
       </c>
@@ -987,13 +1000,14 @@
           <t>ARR</t>
         </is>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="6">
         <f>B13*12</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1001,7 +1015,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1038,8 +1052,8 @@
           <t>Monthly net burn (with new hires)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>60000</v>
+      <c r="B5" s="5" t="n">
+        <v>105000</v>
       </c>
     </row>
     <row r="6">
@@ -1065,39 +1079,38 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pre-money valuation</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+          <t>Cash in the bank</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Post-money valuation (or SAFE cap)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Raise</t>
-        </is>
-      </c>
-      <c r="B11" s="5">
-        <f>B5*(B6+B7)</f>
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Post-money valuation</t>
-        </is>
-      </c>
-      <c r="B12" s="5">
-        <f>B8+B11</f>
+          <t>Raise</t>
+        </is>
+      </c>
+      <c r="B12" s="6">
+        <f>B5*(B6+B7)-B8</f>
         <v/>
       </c>
     </row>
@@ -1107,13 +1120,13 @@
           <t>Dilution</t>
         </is>
       </c>
-      <c r="B13" s="5">
-        <f>B11/B12</f>
+      <c r="B13" s="15">
+        <f>B12/B9</f>
         <v/>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15% to 25% is typical for a seed round</t>
+          <t>15% to 25% is typical for an early round</t>
         </is>
       </c>
     </row>
@@ -1123,13 +1136,14 @@
           <t>Founders keep</t>
         </is>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="15">
         <f>1-B13</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1137,7 +1151,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1169,120 +1183,120 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Score (0-10)</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>What would raise it</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Value proposition</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="9" t="inlineStr"/>
+      <c r="C7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="9" t="inlineStr"/>
+      <c r="C8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Go-to-market</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="9" t="inlineStr"/>
+      <c r="C9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="9" t="inlineStr"/>
+      <c r="C10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="9" t="inlineStr"/>
+      <c r="C11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="9" t="inlineStr"/>
+      <c r="C12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Risks</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="9" t="inlineStr"/>
+      <c r="C13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Milestones</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="9" t="inlineStr"/>
+      <c r="C14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Exit</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="9" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1290,7 +1304,7 @@
           <t>Lowest score</t>
         </is>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="16">
         <f>MIN(B7:B15)</f>
         <v/>
       </c>
@@ -1312,12 +1326,13 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Verdict: ready / ready with conditions / not yet</t>
+          <t>Ready to pitch? Yes, or fix the lowest score first</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1325,7 +1340,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1357,75 +1372,76 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Money released</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Milestone that releases the next gate</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Date to check</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Number that counts as success</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Rule for a miss</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Stage 1</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr"/>
-      <c r="C7" s="9" t="inlineStr"/>
-      <c r="D7" s="9" t="inlineStr"/>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="9" t="inlineStr"/>
+      <c r="B7" s="10" t="inlineStr"/>
+      <c r="C7" s="10" t="inlineStr"/>
+      <c r="D7" s="10" t="inlineStr"/>
+      <c r="E7" s="10" t="inlineStr"/>
+      <c r="F7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Stage 2</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr"/>
-      <c r="C8" s="9" t="inlineStr"/>
-      <c r="D8" s="9" t="inlineStr"/>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="9" t="inlineStr"/>
+      <c r="B8" s="10" t="inlineStr"/>
+      <c r="C8" s="10" t="inlineStr"/>
+      <c r="D8" s="10" t="inlineStr"/>
+      <c r="E8" s="10" t="inlineStr"/>
+      <c r="F8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Stage 3</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr"/>
-      <c r="C9" s="9" t="inlineStr"/>
-      <c r="D9" s="9" t="inlineStr"/>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="9" t="inlineStr"/>
+      <c r="B9" s="10" t="inlineStr"/>
+      <c r="C9" s="10" t="inlineStr"/>
+      <c r="D9" s="10" t="inlineStr"/>
+      <c r="E9" s="10" t="inlineStr"/>
+      <c r="F9" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1433,7 +1449,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1465,40 +1481,41 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Number to watch</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Date to check</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Level that counts as a miss</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Fallback plan</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr"/>
-      <c r="B7" s="9" t="inlineStr"/>
-      <c r="C7" s="9" t="inlineStr"/>
-      <c r="D7" s="9" t="inlineStr"/>
+      <c r="A7" s="10" t="inlineStr"/>
+      <c r="B7" s="10" t="inlineStr"/>
+      <c r="C7" s="10" t="inlineStr"/>
+      <c r="D7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr"/>
-      <c r="B8" s="9" t="inlineStr"/>
-      <c r="C8" s="9" t="inlineStr"/>
-      <c r="D8" s="9" t="inlineStr"/>
+      <c r="A8" s="10" t="inlineStr"/>
+      <c r="B8" s="10" t="inlineStr"/>
+      <c r="C8" s="10" t="inlineStr"/>
+      <c r="D8" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/templates/innovation-calculators.xlsx
+++ b/templates/innovation-calculators.xlsx
@@ -792,7 +792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -911,96 +911,128 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Share of new customers from paid channels (0-1)</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CAC</t>
-        </is>
-      </c>
-      <c r="B16" s="6">
-        <f>B8/B9</f>
-        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LTV</t>
+          <t>Blended CAC</t>
         </is>
       </c>
       <c r="B17" s="6">
-        <f>(B5*B6)/B7</f>
+        <f>B8/B9</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LTV ÷ CAC</t>
-        </is>
-      </c>
-      <c r="B18" s="13">
-        <f>B17/B16</f>
-        <v/>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>3 or more is the usual benchmark</t>
-        </is>
+          <t>Paid CAC</t>
+        </is>
+      </c>
+      <c r="B18" s="6">
+        <f>B8/(B9*B14)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CAC payback (months)</t>
-        </is>
-      </c>
-      <c r="B19" s="14">
-        <f>B16/(B5*B6)</f>
-        <v/>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>under 12 strong, under 18 acceptable</t>
-        </is>
+          <t>LTV</t>
+        </is>
+      </c>
+      <c r="B19" s="6">
+        <f>(B5*B6)/B7</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Net burn per month</t>
-        </is>
-      </c>
-      <c r="B20" s="6">
-        <f>B12-B11</f>
-        <v/>
+          <t>LTV ÷ blended CAC</t>
+        </is>
+      </c>
+      <c r="B20" s="13">
+        <f>B19/B17</f>
+        <v/>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3 or more is the usual benchmark</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Runway (months)</t>
-        </is>
-      </c>
-      <c r="B21" s="14">
-        <f>B10/B20</f>
+          <t>LTV ÷ paid CAC</t>
+        </is>
+      </c>
+      <c r="B21" s="13">
+        <f>B19/B18</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Blended CAC payback (months)</t>
+        </is>
+      </c>
+      <c r="B22" s="14">
+        <f>B17/(B5*B6)</f>
+        <v/>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>under 12 strong, under 18 acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Net burn per month</t>
+        </is>
+      </c>
+      <c r="B23" s="6">
+        <f>B12-B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Runway (months)</t>
+        </is>
+      </c>
+      <c r="B24" s="14">
+        <f>B10/B23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>ARR</t>
         </is>
       </c>
-      <c r="B22" s="6">
+      <c r="B25" s="6">
         <f>B13*12</f>
         <v/>
       </c>

--- a/templates/innovation-calculators.xlsx
+++ b/templates/innovation-calculators.xlsx
@@ -11,9 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riskiest Assumption" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Startup Metrics" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sizing the Raise" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investor Readiness" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spending Gates" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pivot Triggers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spending Gates" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pivot Triggers" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -101,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,7 +117,6 @@
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -482,7 +480,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -595,7 +593,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -603,7 +600,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -782,7 +779,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -790,7 +786,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1039,7 +1035,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1047,7 +1042,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1175,7 +1170,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1183,196 +1177,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Investor Readiness</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Yellow cells are inputs. Blue cells calculate. Replace the example numbers with your own.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Score each area out of 10. Anything below 5 needs fixing before you pitch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Score (0-10)</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>What would raise it</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Value proposition</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="10" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Market</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Go-to-market</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="10" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="10" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="10" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Risks</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" s="10" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Milestones</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Exit</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" s="10" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Lowest score</t>
-        </is>
-      </c>
-      <c r="B17" s="16">
-        <f>MIN(B7:B15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Investor's biggest objection (one sentence)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Your answer (two sentences)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Ready to pitch? Yes, or fix the lowest score first</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1473,15 +1278,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1548,6 +1352,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/templates/innovation-calculators.xlsx
+++ b/templates/innovation-calculators.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market Sizing" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riskiest Assumption" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Startup Metrics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start-up Metrics" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sizing the Raise" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spending Gates" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pivot Triggers" sheetId="6" state="visible" r:id="rId6"/>
@@ -799,7 +799,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Startup Metrics</t>
+          <t>Start-up Metrics</t>
         </is>
       </c>
     </row>
